--- a/Result/checksun_type/裝置_器材零組件.xlsx
+++ b/Result/checksun_type/裝置_器材零組件.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>17.53</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>18.24</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>18.83</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>18.83</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>275.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>134</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>113.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>150.4</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>150.4</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>5.094059701290561</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>275</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>275.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>17.7</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>18.32</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>18.87</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>18.87</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>19.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>93.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>93.40000000000001</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>88.3</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>152.68</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>152.68</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-9.995558126169087</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>19</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>17.61</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>18.37</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>18.37</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>18.9</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>18.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>128.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>128.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>97.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>152.7</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>152.7</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-3.766599375176838</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>18</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>17.77</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>18.43</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>18.93</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>18.93</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>231.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>129.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>129.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>109.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>153.1</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>153.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>5.373577389639848</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>231</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>231.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>17.98</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>18.52</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>18.95</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>127.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>112.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>112.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>104.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>149.36</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>149.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-4.582369281680613</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>127</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>18.31</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>18.64</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>18.99</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>18.99</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>72.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>92.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>92.40000000000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>97.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>147.2</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>147.2</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-7.498637052078394</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>72</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>18.51</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>18.74</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>19.01</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>196.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>83.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>83.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>97.4</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>147.56</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>147.56</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-5.504068257929575</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>196</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,21 +4067,17 @@
           <t>18.81</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AM9" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>19.04</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
       <c r="AP9" t="inlineStr">
         <is>
           <t>12.53</t>
@@ -4164,20 +4118,16 @@
           <t>22.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>66.59999999999999</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>98.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>145.88</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>145.88</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-15.74382468564805</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>22</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,21 +4497,17 @@
           <t>18.83</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>18.92</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AM10" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="AO10" t="inlineStr">
         <is>
           <t>19.04</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
       <c r="AP10" t="inlineStr">
         <is>
           <t>21.95</t>
@@ -4600,20 +4548,16 @@
           <t>146.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>89.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>105.7</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>149.38</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>149.38</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-11.1669115579013</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>146</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>18.78</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>18.96</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>19.03</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>26.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>96.59999999999999</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>109.6</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>148.46</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>148.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-17.51536024833804</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>26</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>18.66</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>19.03</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>26.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>103.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>103.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>112.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>149.84</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>149.84</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-13.10188122580702</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>26</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>19.4</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>21.11</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>23.39</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>23.39</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>1864.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>2337.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>2337.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>3229.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>2177.06</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>2177.06</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-77.28029424114766</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>1864</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>1864.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>19.13</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>23.5</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>3415.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>2350.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>2350.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>3896.6</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>2150.72</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>2150.72</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>13.59225333786071</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>3415</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>3415.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>18.98</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>21.44</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>23.62</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>23.62</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>2213.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>2870.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>2870.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>3772.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>2131.78</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>2131.78</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-23.25383059705064</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>2213</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2213.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>19.12</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>21.69</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>23.75</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>2270.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>2809.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>2809</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>3730.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>2120.7</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>2120.7</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>53.72511487439942</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>2270</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>2270.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>19.37</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>21.94</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>23.88</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>23.88</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>1925.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>3642.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>3642.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>3893.0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>2106.56</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>2106.56</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>155.669140016671</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>1925</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>1925.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>19.63</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>22.17</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>24.02</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>24.02</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>1931.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>4121.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>4121</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>3988.8</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>2188.6</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>2188.6</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>332.7081352193209</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>1931</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>1931.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>19.99</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>22.39</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>24.16</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>22.39</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>24.16</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>6013.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>5442.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>5442.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>3994.5</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>2198.5</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>2198.5</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>573.0956949652737</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>6013</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>6013.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>20.67</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>22.63</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>24.3</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>22.63</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>24.3</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>1906.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>4674.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>4674.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>3467.0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>2083.58</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>2083.58</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>458.6816483535881</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>1906</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>1906.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>21.17</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>22.83</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>24.42</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>22.83</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>24.42</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>6436.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>4651.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>4651.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>3442.0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>2083.48</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>2083.48</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>718.88723718141</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>6436</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>6436.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>21.65</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>23.02</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>24.55</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>24.55</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>4319.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>4143.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>4143.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>2835.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>1990.0</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>1990</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>579.577819893248</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>4319</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>4319.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>22.26</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>24.67</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>24.67</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>8538.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>3856.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>3856.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>2560.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>1948.68</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>1948.68</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>586.6865873425436</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>8538</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>8538.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10463,11 +10331,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>2459</t>
@@ -10649,41 +10513,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT24" t="inlineStr">
         <is>
           <t>0</t>
@@ -10704,20 +10564,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>0</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>0</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10590,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>0</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10759,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10943,11 @@
           <t>27.73</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>27.44</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>27.85</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>27.44</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>27.85</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10994,16 @@
           <t>571.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>548.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>548.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>761.7</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>1293.2</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>1293.2</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11020,10 @@
           <t>-212.8707486559689</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>571</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>571.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11189,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11373,11 @@
           <t>27.66</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>27.42</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>27.9</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11424,16 @@
           <t>58.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>606.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>606</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>836.7</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>1334.3</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>1334.3</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11450,10 @@
           <t>-227.7016548556554</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>58</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11619,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11803,11 @@
           <t>27.71</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>27.41</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>27.98</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>27.98</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11854,16 @@
           <t>206.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>888.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>888.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>878.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>1341.64</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>1341.64</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11880,10 @@
           <t>-185.7921760389343</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>206</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>206.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12049,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12233,11 @@
           <t>27.76</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>27.41</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>28.08</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>28.08</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12284,16 @@
           <t>359.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>1074.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>1074</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>1139.1</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>1341.36</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>1341.36</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12310,10 @@
           <t>-135.1432000136565</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>359</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>359.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12479,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12663,11 @@
           <t>27.78</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>27.43</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>28.17</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>28.17</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12714,16 @@
           <t>1548.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>1035.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>1035.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>1415.2</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>1347.9</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>1347.9</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12740,10 @@
           <t>-74.3538342627719</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>1548</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>1548.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12909,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13093,11 @@
           <t>27.65</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>27.39</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>28.25</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>28.25</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13144,16 @@
           <t>859.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>975.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>975</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1433.1</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>1338.54</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>1338.54</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13170,10 @@
           <t>-112.2492462521234</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>859</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>859.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13339,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13523,11 @@
           <t>27.54</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>27.4</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>28.34</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>28.34</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13574,16 @@
           <t>1469.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>1067.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>1067.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>1385.8</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>1355.24</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>1355.24</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13600,10 @@
           <t>-88.55521887076384</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>1469</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>1469.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13769,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13953,11 @@
           <t>27.37</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>27.41</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>28.43</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>28.43</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14004,16 @@
           <t>1135.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>868.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>868.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>1416.2</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>1339.36</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>1339.36</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14030,10 @@
           <t>-116.9010647948658</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>1135</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>1135.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14199,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14383,11 @@
           <t>27.22000000000001</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>27.42</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>28.51</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>28.51</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14434,16 @@
           <t>167.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>1204.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>1204.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>1608.9</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>1327.5</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>1327.5</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14460,10 @@
           <t>-117.4343780866232</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>167</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14629,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14813,11 @@
           <t>27.18</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>27.46</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>28.59</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>27.46</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>28.59</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14864,16 @@
           <t>1245.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>1794.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>1794.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>1788.5</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>1338.9</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>1338.9</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14890,10 @@
           <t>-10.28788357175472</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>1245</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>1245.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15059,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15243,11 @@
           <t>27.14</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>27.5</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>28.67</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>28.67</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15294,16 @@
           <t>1321.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>1891.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>1891.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>1857.9</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>1338.3</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>1338.3</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15320,10 @@
           <t>27.64596157704864</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>1321</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>1321.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
